--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487827_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487827_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2424</v>
+        <v>4.4185</v>
       </c>
       <c r="E2" t="n">
         <v>2.5752</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6671</v>
+        <v>1.8433</v>
       </c>
       <c r="G2" t="n">
         <v>1.4676</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0254</v>
+        <v>0.1507</v>
       </c>
       <c r="T2" t="n">
         <v>-0.2891</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2636</v>
+        <v>0.4398</v>
       </c>
       <c r="V2" t="n">
         <v>2.1759</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6296</v>
+        <v>3.6258</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0206</v>
+        <v>3.193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6089</v>
+        <v>0.4328</v>
       </c>
       <c r="G3" t="n">
         <v>1.3823</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9846</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1396</v>
+        <v>0.312</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8488</v>
+        <v>0.6727</v>
       </c>
       <c r="V3" t="n">
         <v>1.0508</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.172</v>
+        <v>2.2538</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7391</v>
+        <v>0.7328</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4329</v>
+        <v>1.521</v>
       </c>
       <c r="G4" t="n">
         <v>0.6518</v>
@@ -766,13 +766,13 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9689</v>
+        <v>1.0507</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4378</v>
+        <v>0.4315</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5311</v>
+        <v>0.6192</v>
       </c>
       <c r="V4" t="n">
         <v>0.3432</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0512</v>
+        <v>2.1164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9562</v>
+        <v>1.0214</v>
       </c>
       <c r="F5" t="n">
         <v>1.095</v>
@@ -844,10 +844,10 @@
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2205</v>
+        <v>-0.1553</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8234</v>
+        <v>-0.7581</v>
       </c>
       <c r="U5" t="n">
         <v>0.6029</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6664</v>
+        <v>2.0466</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1159</v>
+        <v>-0.7945</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7824</v>
+        <v>2.8411</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6336000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3125</v>
+        <v>0.6927</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3014</v>
+        <v>0.02</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6139</v>
+        <v>0.6727</v>
       </c>
       <c r="V6" t="n">
         <v>0.5306999999999999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.017</v>
+        <v>0.7589</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1305</v>
+        <v>-0.5706</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1134</v>
+        <v>1.3295</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2367</v>
+        <v>-0.4145</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.049</v>
+        <v>-0.6545</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2857</v>
+        <v>0.24</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.1409</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.3114</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.4523</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2367</v>
+        <v>-0.5553</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.049</v>
+        <v>-0.3431</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2857</v>
+        <v>-0.2123</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2538</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1305</v>
+        <v>0.5372</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1233</v>
+        <v>0.428</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0308</v>
+        <v>0.0259</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2136</v>
+        <v>-0.8396</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1827</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4145</v>
+        <v>-0.9026</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6545</v>
+        <v>0.273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.24</v>
+        <v>-1.1756</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1409</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3114</v>
+        <v>0.1343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4523</v>
+        <v>-0.7144</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5553</v>
+        <v>-0.3225</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3431</v>
+        <v>0.1387</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2123</v>
+        <v>-0.4613</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1755</v>
+        <v>0.3603</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1057</v>
+        <v>-0.0514</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2812</v>
+        <v>0.4117</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.0968</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0448</v>
+        <v>0.0123</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8844</v>
+        <v>-0.1305</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8396</v>
+        <v>0.1428</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6945</v>
+        <v>0.2367</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5033</v>
+        <v>-0.049</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1912</v>
+        <v>0.2857</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7964</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7808</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0156</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1019</v>
+        <v>0.2367</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2775</v>
+        <v>-0.049</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1755</v>
+        <v>0.2857</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8984</v>
+        <v>-0.2244</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0743</v>
+        <v>-0.1305</v>
       </c>
       <c r="U9" t="n">
-        <v>0.824</v>
+        <v>-0.0939</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
+        <v>-0.4353</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.0988</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.6945</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5033</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.1912</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.7964</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.7808</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.0156</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.1755</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.0812</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.6649</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="T10" t="n">
         <v>-0.14</v>
       </c>
-      <c r="E10" t="n">
-        <v>-0.9467</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.8067</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.9026</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.1756</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.5800999999999999</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.1343</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.7144</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.3225</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.1387</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.4613</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.6649</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.2081</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.8731</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.1944</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.1586</v>
-      </c>
       <c r="U10" t="n">
-        <v>0.353</v>
+        <v>0.6479</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0968</v>
+        <v>1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0968</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5152</v>
+        <v>-2.811</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3248</v>
+        <v>-4.4739</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8097</v>
+        <v>1.6629</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2937</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4894</v>
+        <v>1.1936</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6211</v>
+        <v>0.472</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.7216</v>
       </c>
       <c r="V11" t="n">
         <v>1.1215</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.842</v>
+        <v>-3.514</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.657</v>
+        <v>-4.2703</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7563</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6017</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0013</v>
+        <v>0.3293</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4972</v>
+        <v>-0.1105</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4985</v>
+        <v>0.4398</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5767</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.171799999999999</v>
+        <v>8.497900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9818</v>
+        <v>-4.655799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13.1534</v>
+        <v>13.1536</v>
       </c>
       <c r="G13" t="n">
         <v>-2.714500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4901000000000002</v>
+        <v>0.4900999999999993</v>
       </c>
       <c r="I13" t="n">
         <v>-3.2044</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.100499999999999</v>
+        <v>-1.1005</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3657000000000006</v>
+        <v>-0.365700000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-0.7348000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>15.6086</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5291</v>
+        <v>5.8553</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.03310000000000002</v>
+        <v>0.2931</v>
       </c>
       <c r="U13" t="n">
-        <v>5.5621</v>
+        <v>5.5624</v>
       </c>
       <c r="V13" t="n">
         <v>4.3163</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7715</v>
+        <v>4.062</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9449</v>
+        <v>3.3019</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8267</v>
+        <v>0.7601</v>
       </c>
       <c r="G14" t="n">
         <v>2.6649</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3118</v>
+        <v>-0.3977</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0066</v>
+        <v>-0.6495</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3184</v>
+        <v>0.2519</v>
       </c>
       <c r="V14" t="n">
         <v>0.9623</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7291</v>
+        <v>1.0323</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1493</v>
+        <v>-0.0694</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8784</v>
+        <v>1.1017</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6476</v>
+        <v>0.3008</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2214</v>
+        <v>-0.1278</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4262</v>
+        <v>0.4286</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5498</v>
+        <v>0.0192</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1947</v>
+        <v>0.0192</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7446</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0978</v>
+        <v>0.2816</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4162</v>
+        <v>-0.147</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3184</v>
+        <v>0.4286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1618</v>
+        <v>0.1072</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3196</v>
+        <v>-0.0886</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1578</v>
+        <v>0.1957</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9127999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.522</v>
+        <v>0.9823</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1765</v>
+        <v>-1.5503</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6985</v>
+        <v>2.5326</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3008</v>
+        <v>0.7936</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1278</v>
+        <v>0.3902</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4286</v>
+        <v>0.4033</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0192</v>
+        <v>-0.3901</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0192</v>
+        <v>0.2067</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.5968</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2816</v>
+        <v>1.1837</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.147</v>
+        <v>0.1836</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4286</v>
+        <v>1.0001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4032</v>
+        <v>-0.0194</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1957</v>
+        <v>-0.3495</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2075</v>
+        <v>0.3301</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3584</v>
+        <v>0.2838</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6575</v>
+        <v>-0.7922</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0159</v>
+        <v>1.0761</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7936</v>
+        <v>0.6476</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3902</v>
+        <v>0.2214</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4033</v>
+        <v>0.4262</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3901</v>
+        <v>0.5498</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2067</v>
+        <v>-0.1947</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5968</v>
+        <v>0.7446</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1837</v>
+        <v>0.0978</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1836</v>
+        <v>0.4162</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0001</v>
+        <v>-0.3184</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6433</v>
+        <v>-0.2835</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4567</v>
+        <v>-0.3233</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1866</v>
+        <v>0.0398</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>-1.1428</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1461</v>
+        <v>-0.0555</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9879</v>
+        <v>0.5592</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8418</v>
+        <v>-0.6148</v>
       </c>
       <c r="G18" t="n">
         <v>1.4239</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4547</v>
+        <v>0.2531</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1272</v>
+        <v>-0.3014</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3275</v>
+        <v>0.5546</v>
       </c>
       <c r="V18" t="n">
         <v>-2.565</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4582</v>
+        <v>-0.828</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1368</v>
+        <v>-1.7082</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6785</v>
+        <v>0.8801</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7644</v>
@@ -1936,13 +1936,13 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1319</v>
+        <v>-0.5017</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1744</v>
+        <v>-0.7458</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0424</v>
+        <v>0.244</v>
       </c>
       <c r="V19" t="n">
         <v>0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2549</v>
+        <v>-1.6898</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9545</v>
+        <v>-2.8473</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6996</v>
+        <v>1.1575</v>
       </c>
       <c r="G20" t="n">
         <v>0.4803</v>
@@ -2014,13 +2014,13 @@
         <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3596</v>
+        <v>-0.7945</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2396</v>
+        <v>-1.1325</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.12</v>
+        <v>0.338</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1598</v>
+        <v>-2.8256</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7276</v>
+        <v>-3.6204</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5678</v>
+        <v>0.7948</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8038999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4025</v>
+        <v>-0.0683</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9134</v>
+        <v>-0.8062</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5109</v>
+        <v>0.7379</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9127999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7534</v>
+        <v>-2.9509</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.174</v>
+        <v>-4.7454</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4206</v>
+        <v>1.7944</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5905</v>
@@ -2170,13 +2170,13 @@
         <v>2.2893</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6715</v>
+        <v>-0.869</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3049</v>
+        <v>-0.8762</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3666</v>
+        <v>0.0072</v>
       </c>
       <c r="V22" t="n">
         <v>2.5898</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0724</v>
+        <v>-3.3247</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1101</v>
+        <v>-1.6814</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9623</v>
+        <v>-1.6433</v>
       </c>
       <c r="G23" t="n">
         <v>0.5621</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8455</v>
+        <v>-0.0979</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7177</v>
+        <v>-0.2891</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1278</v>
+        <v>0.1912</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5403</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.171600000000002</v>
+        <v>-5.314099999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-13.1535</v>
       </c>
       <c r="F24" t="n">
-        <v>4.9819</v>
+        <v>7.8392</v>
       </c>
       <c r="G24" t="n">
         <v>2.7144</v>
@@ -2326,13 +2326,13 @@
         <v>14.5684</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.5292</v>
+        <v>-2.6717</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.5622</v>
+        <v>-5.5621</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03290000000000012</v>
+        <v>2.8904</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3163</v>
